--- a/public/templates/Shablloni-4-Faqe.xlsx
+++ b/public/templates/Shablloni-4-Faqe.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\Graniti\Te Qafa\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\AAB\Viti 3 Semestri 6\Tema-Graniti\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{53322E48-AE39-4A2E-A80C-D7BEE8280C47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89EAF720-98C5-4E35-8EE8-EDD1F8FF131C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -372,7 +372,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -567,13 +567,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
@@ -624,12 +650,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
@@ -719,15 +739,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -737,9 +748,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -761,6 +769,23 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -1084,11 +1109,11 @@
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
       <c r="E1" s="26"/>
-      <c r="F1" s="70" t="s">
+      <c r="F1" s="68" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="71"/>
-      <c r="H1" s="72"/>
+      <c r="G1" s="69"/>
+      <c r="H1" s="70"/>
     </row>
     <row r="2" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="27" t="s">
@@ -1110,11 +1135,11 @@
       <c r="C3" s="31"/>
       <c r="D3" s="23"/>
       <c r="E3" s="30"/>
-      <c r="F3" s="79" t="s">
+      <c r="F3" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="80"/>
-      <c r="H3" s="81"/>
+      <c r="G3" s="87"/>
+      <c r="H3" s="87"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="27"/>
@@ -1122,9 +1147,9 @@
       <c r="C4" s="33"/>
       <c r="D4" s="23"/>
       <c r="E4" s="30"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="80"/>
-      <c r="H4" s="81"/>
+      <c r="F4" s="87"/>
+      <c r="G4" s="87"/>
+      <c r="H4" s="87"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="27"/>
@@ -1132,31 +1157,31 @@
       <c r="C5" s="23"/>
       <c r="D5" s="23"/>
       <c r="E5" s="30"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="35"/>
+      <c r="F5" s="87"/>
+      <c r="G5" s="87"/>
+      <c r="H5" s="87"/>
     </row>
     <row r="6" spans="1:8" ht="21" x14ac:dyDescent="0.4">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="36"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="30"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="87"/>
+      <c r="G6" s="87"/>
+      <c r="H6" s="87"/>
+    </row>
+    <row r="7" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="27"/>
       <c r="B7" s="23"/>
       <c r="C7" s="23"/>
       <c r="D7" s="23"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="40"/>
-      <c r="H7" s="39"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="37"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="24" t="s">
@@ -1166,286 +1191,286 @@
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
       <c r="E8" s="30"/>
-      <c r="F8" s="41" t="s">
+      <c r="F8" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="G8" s="42"/>
-      <c r="H8" s="43" t="s">
+      <c r="G8" s="40"/>
+      <c r="H8" s="41" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="82" t="s">
+      <c r="A9" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="83"/>
-      <c r="C9" s="83"/>
-      <c r="D9" s="83"/>
-      <c r="E9" s="83"/>
+      <c r="B9" s="78"/>
+      <c r="C9" s="78"/>
+      <c r="D9" s="78"/>
+      <c r="E9" s="78"/>
       <c r="F9" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="G9" s="44"/>
-      <c r="H9" s="43" t="s">
+      <c r="G9" s="42"/>
+      <c r="H9" s="41" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="82"/>
-      <c r="B10" s="83"/>
-      <c r="C10" s="83"/>
-      <c r="D10" s="83"/>
-      <c r="E10" s="83"/>
-      <c r="F10" s="23"/>
+      <c r="A10" s="77"/>
+      <c r="B10" s="78"/>
+      <c r="C10" s="78"/>
+      <c r="D10" s="78"/>
+      <c r="E10" s="78"/>
+      <c r="F10" s="27"/>
       <c r="G10" s="30"/>
       <c r="H10" s="30"/>
     </row>
     <row r="11" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="84" t="s">
+      <c r="A11" s="79" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="85"/>
-      <c r="C11" s="85"/>
-      <c r="D11" s="85"/>
-      <c r="E11" s="86"/>
+      <c r="B11" s="89"/>
+      <c r="C11" s="89"/>
+      <c r="D11" s="89"/>
+      <c r="E11" s="80"/>
       <c r="F11" s="23" t="s">
         <v>23</v>
       </c>
       <c r="G11" s="30"/>
-      <c r="H11" s="68" t="s">
+      <c r="H11" s="66" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="84"/>
-      <c r="B12" s="85"/>
-      <c r="C12" s="85"/>
-      <c r="D12" s="85"/>
-      <c r="E12" s="86"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="69"/>
+      <c r="A12" s="90"/>
+      <c r="B12" s="91"/>
+      <c r="C12" s="91"/>
+      <c r="D12" s="91"/>
+      <c r="E12" s="92"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="67"/>
     </row>
     <row r="13" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="25"/>
+      <c r="B13" s="88"/>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
       <c r="E13" s="30"/>
-      <c r="F13" s="73" t="s">
+      <c r="F13" s="71" t="s">
         <v>32</v>
       </c>
-      <c r="G13" s="74"/>
-      <c r="H13" s="75"/>
+      <c r="G13" s="72"/>
+      <c r="H13" s="73"/>
     </row>
     <row r="14" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="47" t="s">
+      <c r="A14" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="40"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
-      <c r="E14" s="39" t="s">
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="37" t="s">
         <v>26</v>
       </c>
-      <c r="F14" s="76"/>
-      <c r="G14" s="77"/>
-      <c r="H14" s="78"/>
+      <c r="F14" s="74"/>
+      <c r="G14" s="75"/>
+      <c r="H14" s="76"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="47" t="s">
+      <c r="A15" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="39"/>
-      <c r="C15" s="40" t="s">
+      <c r="B15" s="37"/>
+      <c r="C15" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39" t="s">
+      <c r="D15" s="37"/>
+      <c r="E15" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="48" t="s">
+      <c r="F15" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="G15" s="49"/>
-      <c r="H15" s="39" t="s">
+      <c r="G15" s="47"/>
+      <c r="H15" s="93" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="67.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="87" t="s">
+      <c r="A16" s="81" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="88"/>
-      <c r="C16" s="88"/>
-      <c r="D16" s="88"/>
-      <c r="E16" s="89"/>
+      <c r="B16" s="82"/>
+      <c r="C16" s="82"/>
+      <c r="D16" s="82"/>
+      <c r="E16" s="83"/>
       <c r="F16" s="23"/>
       <c r="G16" s="30"/>
       <c r="H16" s="30"/>
     </row>
     <row r="17" spans="1:8" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="50"/>
-      <c r="B17" s="51"/>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="52" t="s">
+      <c r="A17" s="48"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="F17" s="53">
+      <c r="F17" s="51">
         <v>55</v>
       </c>
-      <c r="G17" s="54"/>
-      <c r="H17" s="54"/>
+      <c r="G17" s="52"/>
+      <c r="H17" s="52"/>
     </row>
     <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="50"/>
-      <c r="B18" s="51"/>
-      <c r="C18" s="51"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="55" t="s">
+      <c r="A18" s="48"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="F18" s="56"/>
-      <c r="G18" s="57"/>
-      <c r="H18" s="58">
+      <c r="F18" s="54"/>
+      <c r="G18" s="55"/>
+      <c r="H18" s="56">
         <f>F17</f>
         <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="5.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="50"/>
-      <c r="B19" s="51"/>
-      <c r="C19" s="51"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="59"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="61"/>
-      <c r="H19" s="61"/>
+      <c r="A19" s="48"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="49"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="59"/>
     </row>
     <row r="20" spans="1:8" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="90" t="s">
+      <c r="A20" s="84" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="91"/>
-      <c r="C20" s="91"/>
-      <c r="D20" s="91"/>
-      <c r="E20" s="92"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="61"/>
-      <c r="H20" s="61"/>
+      <c r="B20" s="85"/>
+      <c r="C20" s="85"/>
+      <c r="D20" s="85"/>
+      <c r="E20" s="86"/>
+      <c r="F20" s="58"/>
+      <c r="G20" s="59"/>
+      <c r="H20" s="59"/>
     </row>
     <row r="21" spans="1:8" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="90"/>
-      <c r="B21" s="91"/>
-      <c r="C21" s="91"/>
-      <c r="D21" s="91"/>
-      <c r="E21" s="92"/>
-      <c r="F21" s="60"/>
-      <c r="G21" s="61"/>
-      <c r="H21" s="61"/>
+      <c r="A21" s="84"/>
+      <c r="B21" s="85"/>
+      <c r="C21" s="85"/>
+      <c r="D21" s="85"/>
+      <c r="E21" s="86"/>
+      <c r="F21" s="58"/>
+      <c r="G21" s="59"/>
+      <c r="H21" s="59"/>
     </row>
     <row r="22" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="62"/>
-      <c r="B22" s="63"/>
-      <c r="C22" s="63"/>
-      <c r="D22" s="63"/>
-      <c r="E22" s="52" t="s">
+      <c r="A22" s="60"/>
+      <c r="B22" s="61"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="F22" s="53">
+      <c r="F22" s="51">
         <v>325</v>
       </c>
-      <c r="G22" s="54"/>
-      <c r="H22" s="54"/>
+      <c r="G22" s="52"/>
+      <c r="H22" s="52"/>
     </row>
     <row r="23" spans="1:8" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="62"/>
-      <c r="B23" s="63"/>
-      <c r="C23" s="63"/>
-      <c r="D23" s="63"/>
-      <c r="E23" s="55" t="s">
+      <c r="A23" s="60"/>
+      <c r="B23" s="61"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="F23" s="56"/>
-      <c r="G23" s="57"/>
-      <c r="H23" s="58">
+      <c r="F23" s="54"/>
+      <c r="G23" s="55"/>
+      <c r="H23" s="56">
         <f>F22</f>
         <v>325</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="62"/>
-      <c r="B24" s="63"/>
-      <c r="C24" s="63"/>
-      <c r="D24" s="63"/>
-      <c r="E24" s="64"/>
-      <c r="F24" s="60"/>
-      <c r="G24" s="61"/>
-      <c r="H24" s="61"/>
+      <c r="A24" s="60"/>
+      <c r="B24" s="61"/>
+      <c r="C24" s="61"/>
+      <c r="D24" s="61"/>
+      <c r="E24" s="62"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="59"/>
+      <c r="H24" s="59"/>
     </row>
     <row r="25" spans="1:8" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="90" t="s">
+      <c r="A25" s="84" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="91"/>
-      <c r="C25" s="91"/>
-      <c r="D25" s="91"/>
-      <c r="E25" s="92"/>
-      <c r="F25" s="60"/>
-      <c r="G25" s="61"/>
-      <c r="H25" s="61"/>
+      <c r="B25" s="85"/>
+      <c r="C25" s="85"/>
+      <c r="D25" s="85"/>
+      <c r="E25" s="86"/>
+      <c r="F25" s="58"/>
+      <c r="G25" s="59"/>
+      <c r="H25" s="59"/>
     </row>
     <row r="26" spans="1:8" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="90"/>
-      <c r="B26" s="91"/>
-      <c r="C26" s="91"/>
-      <c r="D26" s="91"/>
-      <c r="E26" s="92"/>
-      <c r="F26" s="60"/>
-      <c r="G26" s="61"/>
-      <c r="H26" s="61"/>
+      <c r="A26" s="84"/>
+      <c r="B26" s="85"/>
+      <c r="C26" s="85"/>
+      <c r="D26" s="85"/>
+      <c r="E26" s="86"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="59"/>
+      <c r="H26" s="59"/>
     </row>
     <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="62"/>
-      <c r="B27" s="63"/>
-      <c r="C27" s="63"/>
-      <c r="D27" s="63"/>
-      <c r="E27" s="52" t="s">
+      <c r="A27" s="60"/>
+      <c r="B27" s="61"/>
+      <c r="C27" s="61"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F27" s="53">
+      <c r="F27" s="51">
         <v>35</v>
       </c>
-      <c r="G27" s="54"/>
-      <c r="H27" s="54"/>
+      <c r="G27" s="52"/>
+      <c r="H27" s="52"/>
     </row>
     <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="62"/>
-      <c r="B28" s="63"/>
-      <c r="C28" s="63"/>
-      <c r="D28" s="63"/>
-      <c r="E28" s="55" t="s">
+      <c r="A28" s="60"/>
+      <c r="B28" s="61"/>
+      <c r="C28" s="61"/>
+      <c r="D28" s="61"/>
+      <c r="E28" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="F28" s="56"/>
-      <c r="G28" s="57"/>
-      <c r="H28" s="58">
+      <c r="F28" s="54"/>
+      <c r="G28" s="55"/>
+      <c r="H28" s="56">
         <f>F27</f>
         <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="50"/>
-      <c r="B29" s="51"/>
-      <c r="C29" s="51"/>
-      <c r="D29" s="51"/>
-      <c r="E29" s="52"/>
-      <c r="F29" s="53"/>
-      <c r="G29" s="54"/>
-      <c r="H29" s="54"/>
+      <c r="A29" s="48"/>
+      <c r="B29" s="49"/>
+      <c r="C29" s="49"/>
+      <c r="D29" s="49"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="51"/>
+      <c r="G29" s="52"/>
+      <c r="H29" s="52"/>
     </row>
     <row r="30" spans="1:8" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="9"/>
@@ -1458,38 +1483,38 @@
       <c r="H30" s="19"/>
     </row>
     <row r="31" spans="1:8" ht="1.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="65" t="s">
+      <c r="A31" s="63" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="66"/>
-      <c r="C31" s="66"/>
-      <c r="D31" s="66"/>
-      <c r="E31" s="67"/>
+      <c r="B31" s="64"/>
+      <c r="C31" s="64"/>
+      <c r="D31" s="64"/>
+      <c r="E31" s="65"/>
       <c r="F31" s="1"/>
       <c r="G31" s="2"/>
       <c r="H31" s="6"/>
     </row>
     <row r="32" spans="1:8" ht="60.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="65"/>
-      <c r="B32" s="66"/>
-      <c r="C32" s="66"/>
-      <c r="D32" s="66"/>
-      <c r="E32" s="67"/>
+      <c r="A32" s="63"/>
+      <c r="B32" s="64"/>
+      <c r="C32" s="64"/>
+      <c r="D32" s="64"/>
+      <c r="E32" s="65"/>
       <c r="F32" s="1"/>
       <c r="G32" s="2"/>
       <c r="H32" s="6"/>
     </row>
     <row r="33" spans="1:8" ht="1.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="65"/>
-      <c r="B33" s="66"/>
-      <c r="C33" s="66"/>
-      <c r="D33" s="66"/>
-      <c r="E33" s="67"/>
+      <c r="A33" s="63"/>
+      <c r="B33" s="64"/>
+      <c r="C33" s="64"/>
+      <c r="D33" s="64"/>
+      <c r="E33" s="65"/>
       <c r="F33" s="1"/>
       <c r="G33" s="2"/>
       <c r="H33" s="6"/>
     </row>
-    <row r="34" spans="1:8" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="9"/>
       <c r="B34" s="10"/>
       <c r="C34" s="10"/>
@@ -1513,7 +1538,7 @@
       </c>
       <c r="F35" s="20"/>
       <c r="G35" s="21"/>
-      <c r="H35" s="58">
+      <c r="H35" s="56">
         <f>F34</f>
         <v>1</v>
       </c>
@@ -1594,12 +1619,12 @@
     <mergeCell ref="H11:H12"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="F13:H14"/>
-    <mergeCell ref="F3:H4"/>
     <mergeCell ref="A9:E10"/>
     <mergeCell ref="A11:E12"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A20:E21"/>
     <mergeCell ref="A25:E26"/>
+    <mergeCell ref="F3:H6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="92" orientation="portrait" r:id="rId1"/>
